--- a/public/sap-reporting/expansion-150-downloads/EXT-QM04-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-QM04-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rdf003dbf3dcf4e92"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R65e38941999a49f8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rd5e85015df904bcd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="Rf9da53f0d4e54b49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Rc3626654076c45ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="Rd56f076747514a04"/>
   </x:sheets>
 </x:workbook>
 </file>
